--- a/news_daily/2026-10-05.xlsx
+++ b/news_daily/2026-10-05.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -101,9 +96,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1007,6 +1023,10 @@
       <c r="BF2" s="2" t="inlineStr"/>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1177,6 +1197,10 @@
       <c r="BF3" s="2" t="inlineStr"/>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1335,888 +1359,980 @@
       <c r="BF4" s="2" t="inlineStr"/>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-10-05T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Some Equifax customers could be owed money from a class action settlement. See if you're eligible for a payout</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>'-0.106</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPT2JLdERHNEg1enhzTmU0bXB4cTBRS0FHdWkycUt2ZXlCN0cyQy05c05TTy02QzJiRFo2RmxVejVMRXFQaktwRkNJWkpPOTdzcS1ubkg5VlRaTHhsdVRhbGdzaDNPOFJzQ0h5b25Zcjl5bEl2LWhWcXdpektlSjBuUk8xbEFxc1VqZG05ZE5iNjJUWEx6UnFuak5NdC1keTlwT1J2dVQ4dldKU2JSN29jNnhmYXBJcldaVkVZcDFqdUYxcE1lSzZhNXp1MGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>WTHR</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>04ae91a686d841c9952785c94dee8c49</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>8227192f1365a912f18b4191</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>3695499d0cbb5db2d2b019b2</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>EFX-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>'-0.106</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPT2JLdERHNEg1enhzTmU0bXB4cTBRS0FHdWkycUt2ZXlCN0cyQy05c05TTy02QzJiRFo2RmxVejVMRXFQaktwRkNJWkpPOTdzcS1ubkg5VlRaTHhsdVRhbGdzaDNPOFJzQ0h5b25Zcjl5bEl2LWhWcXdpektlSjBuUk8xbEFxc1VqZG05ZE5iNjJUWEx6UnFuak5NdC1keTlwT1J2dVQ4dldKU2JSN29jNnhmYXBJcldaVkVZcDFqdUYxcE1lSzZhNXp1MGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>WTHR</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>8227192f1365a912f18b4191</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>3695499d0cbb5db2d2b019b2</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-10-05T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Nvidia, Broadcom shielded as AI power crunch hits chip supply chain, says Morgan Stanley</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>供應鏈中斷</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>'-0.799</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOMF9lcTkxVU5OWUp5THhibUJWc3U0MWo5c2dreS02dFk3TGt4SlBXLVdpX0htOV85SnVsc3RUZjZJZDJac3p3bFgzS05uU2hjVXh5N0RjcFVtQml0TnBRSllwREVDdUVFOTBoTTRMT01RMnVUNGQtZk1ZY0ZIdUZHWHNBbjlaMk10dEpJZ3J5eTZHYjlDQW9JdEg4STBBLVNYNlFRb1J1aUJudHJkS2lmT0otSUJHdE5wVnJaXw?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>Reuters</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>SUPPLY_CHAIN_DISRUPTION</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>supply chain</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>4e3dae046853cf51ec09ef5b</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <t>3b6b324abaa675f8751e2233</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>NVDA-SUPPLY_CHAIN_DISRUPTION-001</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>ACN</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2026-10-05T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>EXCLUSIVE: Accenture contractor removed from FBI following damaging data breach, sources say</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>資料外洩</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>'-0.936</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPNnh4WEZTOEFBQUo1TmMzeGNFQ1FPaDQzY21NY0lpMjZJM2tiazlCSG5nb3BsdDVmaHVnc0RzbWpZZG1tUDBJdmNJN3pBcFN0eDdRTTlmZEt2YmZtck1Nc3ZzZTdzd1Ftb3FPNzVHcTFXQ2cxTGdXZHppeTlFUU5lSWxKY3ZmYnFtVWl6eGxueXFGaTBoVHd6WjUxSU80WkMyNE9pTkRHZnVyZ0tEN01pM0tCcHo1ZVdIOUpfRXVQaw?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>Reuters</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>CYBER</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>DATA_BREACH</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>data breach</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>a4907b6d497dd82d98ff73f3</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AD7" s="3" t="inlineStr">
         <is>
           <t>0c94db61ca0b7844387a6c13</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AE7" s="3" t="inlineStr">
         <is>
           <t>ACN-DATA_BREACH-001</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr">
         <is>
           <t>ACN</t>
         </is>
       </c>
-      <c r="BC7" s="4" t="inlineStr">
+      <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="4" t="inlineStr">
+      <c r="BF7" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="4" t="inlineStr">
+      <c r="BG7" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Electronic Arts</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-10-05T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Exclusive | Electronic Arts Bondholders Allege Default Following Largest LBO</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>違約</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>'-0.665</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZnpmM3d6Tjh4SVFKSF9VZ0l0SklwQU5lTmp5MUVSSnBwS0toY3RNdjU0R2thT0d6cVNON1BJaVExTUs3REI0UjgzOUdKcVRZNUZ1ZUZ2aWJZOFNDU1Z2Q1BaZDJOZDQ3bjNwT1ZNNnp2aE5iNlhsSmZYUmJEYlMyVXpfYWszYUk0SElxZmpGcnU2bjMyTFZpck51RGJvaUpIaGpnQ1JNdFBMNXFS?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>f575911bcbe6440ea649d1cd84a6a406</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>2e264a9236da31d2833fd839</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>ff3f385b58f0ac6dc49a5cd1</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>EA-DEFAULT-001</t>
+        </is>
+      </c>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>'-0.665</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZnpmM3d6Tjh4SVFKSF9VZ0l0SklwQU5lTmp5MUVSSnBwS0toY3RNdjU0R2thT0d6cVNON1BJaVExTUs3REI0UjgzOUdKcVRZNUZ1ZUZ2aWJZOFNDU1Z2Q1BaZDJOZDQ3bjNwT1ZNNnp2aE5iNlhsSmZYUmJEYlMyVXpfYWszYUk0SElxZmpGcnU2bjMyTFZpck51RGJvaUpIaGpnQ1JNdFBMNXFS?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="inlineStr"/>
-      <c r="X8" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z8" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA8" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="5" t="inlineStr"/>
-      <c r="AC8" s="5" t="inlineStr">
-        <is>
-          <t>2e264a9236da31d2833fd839</t>
-        </is>
-      </c>
-      <c r="AD8" s="5" t="inlineStr">
-        <is>
-          <t>ff3f385b58f0ac6dc49a5cd1</t>
-        </is>
-      </c>
-      <c r="AE8" s="5" t="inlineStr">
-        <is>
-          <t>EA-DEFAULT-001</t>
-        </is>
-      </c>
-      <c r="AF8" s="5" t="inlineStr"/>
-      <c r="AG8" s="5" t="inlineStr"/>
-      <c r="AH8" s="5" t="inlineStr"/>
-      <c r="AI8" s="5" t="inlineStr"/>
-      <c r="AJ8" s="5" t="inlineStr"/>
-      <c r="AK8" s="5" t="inlineStr"/>
-      <c r="AL8" s="5" t="inlineStr"/>
-      <c r="AM8" s="5" t="inlineStr"/>
-      <c r="AN8" s="5" t="inlineStr"/>
-      <c r="AO8" s="5" t="inlineStr"/>
-      <c r="AP8" s="5" t="inlineStr"/>
-      <c r="AQ8" s="5" t="inlineStr"/>
-      <c r="AR8" s="5" t="inlineStr"/>
-      <c r="AS8" s="5" t="inlineStr"/>
-      <c r="AT8" s="5" t="inlineStr"/>
-      <c r="AU8" s="5" t="inlineStr"/>
-      <c r="AV8" s="5" t="inlineStr"/>
-      <c r="AW8" s="5" t="inlineStr"/>
-      <c r="AX8" s="5" t="inlineStr"/>
-      <c r="AY8" s="5" t="inlineStr"/>
-      <c r="AZ8" s="5" t="inlineStr"/>
-      <c r="BA8" s="5" t="inlineStr"/>
-      <c r="BB8" s="5" t="inlineStr">
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="BC8" s="5" t="inlineStr">
+      <c r="BC8" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="5" t="inlineStr"/>
-      <c r="BE8" s="5" t="inlineStr">
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF8" s="5" t="inlineStr"/>
-      <c r="BG8" s="5" t="inlineStr">
+      <c r="BF8" s="4" t="inlineStr"/>
+      <c r="BG8" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH8" s="5" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>DGX</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Quest Diagnostics Incorporated Common Stock</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-10-05T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>DGX Station GB300 Cluster: Two Towers, Two 400G DACs, and Frontier Models Without the Offload Penalty</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.068</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPeUp5Mnp3VGdiTzdhTGtBRUtfbE9VLUp0N2hNLTBicFVJUGJGSGJmSFM3bklSYkZaNDR4V21Cb21RaHJLdVhEeEowRE0tV1dpTmIzeU1GZzd0b1BCdTlGZ0w0U3JlYURrLWpVbllFV3cxbXp6X3ZNT1NWNzBhY0dCRTMxVzBXXzZNN3pKdnRac0vSAZYBQVVfeXFMTTk5bnh1alFBY3VzUjhTN3FZTldLTFNnRFpLek5pWF8talZ4bGNSRUNGa1RTX05aSkItR3NNQ293R3dWVzVMMzRvb2o4OVBvWUQyb3k3ZndmQ21Ib1hpdzgwclNrR0ZJMm53M1JILW91Q2NjSjNDM2Z5N2ZsY1lXTDAtS1E0dE9jWEl1SFRmUGJTT09Pbk1B?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>StorageReview.com</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>penalty</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>f0d3c7a22f1b4e66b62730df0382c0bc</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>440f06adc93e9e4ccce97a7f</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>a1d98328fad5f13bac00586d</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>DGX-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPeUp5Mnp3VGdiTzdhTGtBRUtfbE9VLUp0N2hNLTBicFVJUGJGSGJmSFM3bklSYkZaNDR4V21Cb21RaHJLdVhEeEowRE0tV1dpTmIzeU1GZzd0b1BCdTlGZ0w0U3JlYURrLWpVbllFV3cxbXp6X3ZNT1NWNzBhY0dCRTMxVzBXXzZNN3pKdnRac0vSAZYBQVVfeXFMTTk5bnh1alFBY3VzUjhTN3FZTldLTFNnRFpLek5pWF8talZ4bGNSRUNGa1RTX05aSkItR3NNQ293R3dWVzVMMzRvb2o4OVBvWUQyb3k3ZndmQ21Ib1hpdzgwclNrR0ZJMm53M1JILW91Q2NjSjNDM2Z5N2ZsY1lXTDAtS1E0dE9jWEl1SFRmUGJTT09Pbk1B?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>StorageReview.com</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>440f06adc93e9e4ccce97a7f</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>a1d98328fad5f13bac00586d</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr">
-        <is>
-          <t>DGX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr">
         <is>
           <t>DGX</t>
         </is>
       </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr">
+      <c r="BF9" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BG9" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2375,9 +2491,13 @@
       <c r="BF10" s="2" t="inlineStr"/>
       <c r="BG10" s="2" t="inlineStr"/>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH10"/>
+  <autoFilter ref="A1:BL10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2388,7 +2508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2451,6 +2571,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2754,6 +2878,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2768,12 +2912,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Equifax, Inc. Common Stock</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2783,23 +2927,23 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Some Equifax customers could be owed money from a class action settlement. See if you're eligible for a payout</t>
+          <t>Nvidia, Broadcom shielded as AI power crunch hits chip supply chain, says Morgan Stanley</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>供應鏈中斷</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -2820,7 +2964,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>'-0.106</t>
+          <t>'-0.799</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -2834,28 +2978,28 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPT2JLdERHNEg1enhzTmU0bXB4cTBRS0FHdWkycUt2ZXlCN0cyQy05c05TTy02QzJiRFo2RmxVejVMRXFQaktwRkNJWkpPOTdzcS1ubkg5VlRaTHhsdVRhbGdzaDNPOFJzQ0h5b25Zcjl5bEl2LWhWcXdpektlSjBuUk8xbEFxc1VqZG05ZE5iNjJUWEx6UnFuak5NdC1keTlwT1J2dVQ4dldKU2JSN29jNnhmYXBJcldaVkVZcDFqdUYxcE1lSzZhNXp1MGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOMF9lcTkxVU5OWUp5THhibUJWc3U0MWo5c2dreS02dFk3TGt4SlBXLVdpX0htOV85SnVsc3RUZjZJZDJac3p3bFgzS05uU2hjVXh5N0RjcFVtQml0TnBRSllwREVDdUVFOTBoTTRMT01RMnVUNGQtZk1ZY0ZIdUZHWHNBbjlaMk10dEpJZ3J5eTZHYjlDQW9JdEg4STBBLVNYNlFRb1J1aUJudHJkS2lmT0otSUJHdE5wVnJaXw?oc=5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>WTHR</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr"/>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>supply chain</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
@@ -2866,17 +3010,17 @@
       <c r="AB2" s="3" t="inlineStr"/>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>8227192f1365a912f18b4191</t>
+          <t>4e3dae046853cf51ec09ef5b</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>3695499d0cbb5db2d2b019b2</t>
+          <t>3b6b324abaa675f8751e2233</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr">
         <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
+          <t>NVDA-SUPPLY_CHAIN_DISRUPTION-001</t>
         </is>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
@@ -2898,7 +3042,7 @@
       <c r="AV2" s="3" t="inlineStr"/>
       <c r="AW2" s="3" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX2" s="3" t="inlineStr"/>
@@ -2907,7 +3051,7 @@
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
@@ -2918,12 +3062,12 @@
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG2" s="3" t="inlineStr">
@@ -2932,184 +3076,192 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2026-10-05T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Nvidia, Broadcom shielded as AI power crunch hits chip supply chain, says Morgan Stanley</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>EXCLUSIVE: Accenture contractor removed from FBI following damaging data breach, sources say</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>'-0.799</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>'-0.936</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOMF9lcTkxVU5OWUp5THhibUJWc3U0MWo5c2dreS02dFk3TGt4SlBXLVdpX0htOV85SnVsc3RUZjZJZDJac3p3bFgzS05uU2hjVXh5N0RjcFVtQml0TnBRSllwREVDdUVFOTBoTTRMT01RMnVUNGQtZk1ZY0ZIdUZHWHNBbjlaMk10dEpJZ3J5eTZHYjlDQW9JdEg4STBBLVNYNlFRb1J1aUJudHJkS2lmT0otSUJHdE5wVnJaXw?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPNnh4WEZTOEFBQUo1TmMzeGNFQ1FPaDQzY21NY0lpMjZJM2tiazlCSG5nb3BsdDVmaHVnc0RzbWpZZG1tUDBJdmNJN3pBcFN0eDdRTTlmZEt2YmZtck1Nc3ZzZTdzd1Ftb3FPNzVHcTFXQ2cxTGdXZHppeTlFUU5lSWxKY3ZmYnFtVWl6eGxueXFGaTBoVHd6WjUxSU80WkMyNE9pTkRHZnVyZ0tEN01pM0tCcHo1ZVdIOUpfRXVQaw?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>Reuters</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>4e3dae046853cf51ec09ef5b</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>3b6b324abaa675f8751e2233</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr">
-        <is>
-          <t>NVDA-SUPPLY_CHAIN_DISRUPTION-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>a4907b6d497dd82d98ff73f3</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>0c94db61ca0b7844387a6c13</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>ACN-DATA_BREACH-001</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="4" t="inlineStr"/>
-      <c r="BE3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="4" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr"/>
+      <c r="BE3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3124,12 +3276,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3139,34 +3291,38 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Accenture contractor removed from FBI following damaging data breach, sources say</t>
+          <t>Exclusive | Electronic Arts Bondholders Allege Default Following Largest LBO</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>資料外洩</t>
+          <t>違約</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -3176,7 +3332,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>'-0.936</t>
+          <t>'-0.665</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr"/>
@@ -3190,28 +3346,28 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPNnh4WEZTOEFBQUo1TmMzeGNFQ1FPaDQzY21NY0lpMjZJM2tiazlCSG5nb3BsdDVmaHVnc0RzbWpZZG1tUDBJdmNJN3pBcFN0eDdRTTlmZEt2YmZtck1Nc3ZzZTdzd1Ftb3FPNzVHcTFXQ2cxTGdXZHppeTlFUU5lSWxKY3ZmYnFtVWl6eGxueXFGaTBoVHd6WjUxSU80WkMyNE9pTkRHZnVyZ0tEN01pM0tCcHo1ZVdIOUpfRXVQaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZnpmM3d6Tjh4SVFKSF9VZ0l0SklwQU5lTmp5MUVSSnBwS0toY3RNdjU0R2thT0d6cVNON1BJaVExTUs3REI0UjgzOUdKcVRZNUZ1ZUZ2aWJZOFNDU1Z2Q1BaZDJOZDQ3bjNwT1ZNNnp2aE5iNlhsSmZYUmJEYlMyVXpfYWszYUk0SElxZmpGcnU2bjMyTFZpck51RGJvaUpIaGpnQ1JNdFBMNXFS?oc=5</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>CYBER</t>
+          <t>FINANCIAL</t>
         </is>
       </c>
       <c r="Y4" s="4" t="inlineStr">
         <is>
-          <t>DATA_BREACH</t>
+          <t>DEFAULT</t>
         </is>
       </c>
       <c r="Z4" s="4" t="inlineStr">
         <is>
-          <t>data breach</t>
+          <t>default</t>
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr">
@@ -3219,20 +3375,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>f575911bcbe6440ea649d1cd84a6a406</t>
+        </is>
+      </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
-          <t>a4907b6d497dd82d98ff73f3</t>
+          <t>2e264a9236da31d2833fd839</t>
         </is>
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
-          <t>0c94db61ca0b7844387a6c13</t>
+          <t>ff3f385b58f0ac6dc49a5cd1</t>
         </is>
       </c>
       <c r="AE4" s="4" t="inlineStr">
         <is>
-          <t>ACN-DATA_BREACH-001</t>
+          <t>EA-DEFAULT-001</t>
         </is>
       </c>
       <c r="AF4" s="4" t="inlineStr"/>
@@ -3244,7 +3404,11 @@
       <c r="AL4" s="4" t="inlineStr"/>
       <c r="AM4" s="4" t="inlineStr"/>
       <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="4" t="inlineStr"/>
       <c r="AQ4" s="4" t="inlineStr"/>
       <c r="AR4" s="4" t="inlineStr"/>
@@ -3252,18 +3416,14 @@
       <c r="AT4" s="4" t="inlineStr"/>
       <c r="AU4" s="4" t="inlineStr"/>
       <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW4" s="4" t="inlineStr"/>
       <c r="AX4" s="4" t="inlineStr"/>
       <c r="AY4" s="4" t="inlineStr"/>
       <c r="AZ4" s="4" t="inlineStr"/>
       <c r="BA4" s="4" t="inlineStr"/>
       <c r="BB4" s="4" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="BC4" s="4" t="inlineStr">
@@ -3274,371 +3434,31 @@
       <c r="BD4" s="4" t="inlineStr"/>
       <c r="BE4" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF4" s="4" t="inlineStr"/>
       <c r="BG4" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-05T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Exclusive | Electronic Arts Bondholders Allege Default Following Largest LBO</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>'-0.665</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZnpmM3d6Tjh4SVFKSF9VZ0l0SklwQU5lTmp5MUVSSnBwS0toY3RNdjU0R2thT0d6cVNON1BJaVExTUs3REI0UjgzOUdKcVRZNUZ1ZUZ2aWJZOFNDU1Z2Q1BaZDJOZDQ3bjNwT1ZNNnp2aE5iNlhsSmZYUmJEYlMyVXpfYWszYUk0SElxZmpGcnU2bjMyTFZpck51RGJvaUpIaGpnQ1JNdFBMNXFS?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z5" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA5" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="5" t="inlineStr"/>
-      <c r="AC5" s="5" t="inlineStr">
-        <is>
-          <t>2e264a9236da31d2833fd839</t>
-        </is>
-      </c>
-      <c r="AD5" s="5" t="inlineStr">
-        <is>
-          <t>ff3f385b58f0ac6dc49a5cd1</t>
-        </is>
-      </c>
-      <c r="AE5" s="5" t="inlineStr">
-        <is>
-          <t>EA-DEFAULT-001</t>
-        </is>
-      </c>
-      <c r="AF5" s="5" t="inlineStr"/>
-      <c r="AG5" s="5" t="inlineStr"/>
-      <c r="AH5" s="5" t="inlineStr"/>
-      <c r="AI5" s="5" t="inlineStr"/>
-      <c r="AJ5" s="5" t="inlineStr"/>
-      <c r="AK5" s="5" t="inlineStr"/>
-      <c r="AL5" s="5" t="inlineStr"/>
-      <c r="AM5" s="5" t="inlineStr"/>
-      <c r="AN5" s="5" t="inlineStr"/>
-      <c r="AO5" s="5" t="inlineStr"/>
-      <c r="AP5" s="5" t="inlineStr"/>
-      <c r="AQ5" s="5" t="inlineStr"/>
-      <c r="AR5" s="5" t="inlineStr"/>
-      <c r="AS5" s="5" t="inlineStr"/>
-      <c r="AT5" s="5" t="inlineStr"/>
-      <c r="AU5" s="5" t="inlineStr"/>
-      <c r="AV5" s="5" t="inlineStr"/>
-      <c r="AW5" s="5" t="inlineStr"/>
-      <c r="AX5" s="5" t="inlineStr"/>
-      <c r="AY5" s="5" t="inlineStr"/>
-      <c r="AZ5" s="5" t="inlineStr"/>
-      <c r="BA5" s="5" t="inlineStr"/>
-      <c r="BB5" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="BC5" s="5" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD5" s="5" t="inlineStr"/>
-      <c r="BE5" s="5" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="5" t="inlineStr"/>
-      <c r="BG5" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Quest Diagnostics Incorporated Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>DGX Station GB300 Cluster: Two Towers, Two 400G DACs, and Frontier Models Without the Offload Penalty</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPeUp5Mnp3VGdiTzdhTGtBRUtfbE9VLUp0N2hNLTBicFVJUGJGSGJmSFM3bklSYkZaNDR4V21Cb21RaHJLdVhEeEowRE0tV1dpTmIzeU1GZzd0b1BCdTlGZ0w0U3JlYURrLWpVbllFV3cxbXp6X3ZNT1NWNzBhY0dCRTMxVzBXXzZNN3pKdnRac0vSAZYBQVVfeXFMTTk5bnh1alFBY3VzUjhTN3FZTldLTFNnRFpLek5pWF8talZ4bGNSRUNGa1RTX05aSkItR3NNQ293R3dWVzVMMzRvb2o4OVBvWUQyb3k3ZndmQ21Ib1hpdzgwclNrR0ZJMm53M1JILW91Q2NjSjNDM2Z5N2ZsY1lXTDAtS1E0dE9jWEl1SFRmUGJTT09Pbk1B?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>StorageReview.com</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>440f06adc93e9e4ccce97a7f</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>a1d98328fad5f13bac00586d</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>DGX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH6"/>
+  <autoFilter ref="A1:BL4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3649,7 +3469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3712,6 +3532,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4013,6 +3837,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -4185,6 +4029,10 @@
       <c r="BF2" s="2" t="inlineStr"/>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4355,9 +4203,13 @@
       <c r="BF3" s="2" t="inlineStr"/>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH3"/>
+  <autoFilter ref="A1:BL3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4368,7 +4220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4431,6 +4283,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4734,9 +4590,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4747,7 +4623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4797,134 +4673,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4934,46 +4810,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4982,12 +4892,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4997,90 +4907,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5090,94 +5004,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5185,89 +5099,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-05.xlsx
+++ b/news_daily/2026-10-05.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -865,7 +865,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>NXP Semiconductors</t>
@@ -899,17 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -962,7 +966,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>e373d96782514138840087972bfd6cbf</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>3de0fe66180c3ba2bf7ad865</t>
@@ -989,7 +997,7 @@
       <c r="AN2" s="2" t="inlineStr"/>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr"/>
@@ -1023,10 +1031,22 @@
       <c r="BF2" s="2" t="inlineStr"/>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1039,7 +1059,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>BNY Mellon</t>
@@ -1073,17 +1097,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1136,7 +1160,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>d2d807a7bdc040aeaf77854d55f04d4c</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>76d272247f249b3762e4eca7</t>
@@ -1163,7 +1191,7 @@
       <c r="AN3" s="2" t="inlineStr"/>
       <c r="AO3" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP3" s="2" t="inlineStr"/>
@@ -1197,10 +1225,22 @@
       <c r="BF3" s="2" t="inlineStr"/>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1571,186 +1611,210 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-05T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Nvidia, Broadcom shielded as AI power crunch hits chip supply chain, says Morgan Stanley</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>'-0.799</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOMF9lcTkxVU5OWUp5THhibUJWc3U0MWo5c2dreS02dFk3TGt4SlBXLVdpX0htOV85SnVsc3RUZjZJZDJac3p3bFgzS05uU2hjVXh5N0RjcFVtQml0TnBRSllwREVDdUVFOTBoTTRMT01RMnVUNGQtZk1ZY0ZIdUZHWHNBbjlaMk10dEpJZ3J5eTZHYjlDQW9JdEg4STBBLVNYNlFRb1J1aUJudHJkS2lmT0otSUJHdE5wVnJaXw?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>545474e94d834c4daad06ea00f99c5d9</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>4e3dae046853cf51ec09ef5b</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>3b6b324abaa675f8751e2233</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>NVDA-SUPPLY_CHAIN_DISRUPTION-001</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>'-0.799</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOMF9lcTkxVU5OWUp5THhibUJWc3U0MWo5c2dreS02dFk3TGt4SlBXLVdpX0htOV85SnVsc3RUZjZJZDJac3p3bFgzS05uU2hjVXh5N0RjcFVtQml0TnBRSllwREVDdUVFOTBoTTRMT01RMnVUNGQtZk1ZY0ZIdUZHWHNBbjlaMk10dEpJZ3J5eTZHYjlDQW9JdEg4STBBLVNYNlFRb1J1aUJudHJkS2lmT0otSUJHdE5wVnJaXw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>4e3dae046853cf51ec09ef5b</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>3b6b324abaa675f8751e2233</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>NVDA-SUPPLY_CHAIN_DISRUPTION-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1801,13 +1865,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1860,7 +1928,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>4e74d062a59940418686a4478b7b9cac</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>a4907b6d497dd82d98ff73f3</t>
@@ -1885,7 +1957,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -1931,8 +2007,16 @@
       <c r="BH7" s="3" t="inlineStr"/>
       <c r="BI7" s="3" t="inlineStr"/>
       <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2503,967 +2587,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:BL4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="65" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="22" customWidth="1" min="29" max="29"/>
-    <col width="22" customWidth="1" min="30" max="30"/>
-    <col width="22" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
-    <col width="22" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
-    <col width="22" customWidth="1" min="36" max="36"/>
-    <col width="22" customWidth="1" min="37" max="37"/>
-    <col width="22" customWidth="1" min="38" max="38"/>
-    <col width="22" customWidth="1" min="39" max="39"/>
-    <col width="65" customWidth="1" min="40" max="40"/>
-    <col width="22" customWidth="1" min="41" max="41"/>
-    <col width="22" customWidth="1" min="42" max="42"/>
-    <col width="22" customWidth="1" min="43" max="43"/>
-    <col width="22" customWidth="1" min="44" max="44"/>
-    <col width="22" customWidth="1" min="45" max="45"/>
-    <col width="22" customWidth="1" min="46" max="46"/>
-    <col width="22" customWidth="1" min="47" max="47"/>
-    <col width="22" customWidth="1" min="48" max="48"/>
-    <col width="22" customWidth="1" min="49" max="49"/>
-    <col width="22" customWidth="1" min="50" max="50"/>
-    <col width="22" customWidth="1" min="51" max="51"/>
-    <col width="22" customWidth="1" min="52" max="52"/>
-    <col width="22" customWidth="1" min="53" max="53"/>
-    <col width="22" customWidth="1" min="54" max="54"/>
-    <col width="22" customWidth="1" min="55" max="55"/>
-    <col width="22" customWidth="1" min="56" max="56"/>
-    <col width="22" customWidth="1" min="57" max="57"/>
-    <col width="22" customWidth="1" min="58" max="58"/>
-    <col width="22" customWidth="1" min="59" max="59"/>
-    <col width="22" customWidth="1" min="60" max="60"/>
-    <col width="22" customWidth="1" min="61" max="61"/>
-    <col width="22" customWidth="1" min="62" max="62"/>
-    <col width="22" customWidth="1" min="63" max="63"/>
-    <col width="22" customWidth="1" min="64" max="64"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Published Time</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>中文摘要</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>事件中文</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>最終判斷來源</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>分類狀態</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>已人工覆核</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>來源方法</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>FinBERT</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Rule_Event_Code</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Rule_Level</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>LLM事件代碼</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>LLM辨識公司</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker來源</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Title_ZH</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Event_type</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Event_Code</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Keyword</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>曝險金額</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>人工版本</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>article_id</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>news_id</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Event_ID</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>監控池</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Keyword候選</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Keyword事件代碼</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>LLM狀態</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>事件狀態</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Confirmed_Default</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>需要人工覆核</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>LLM模型</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Prompt版本</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>input_tokens</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>API錯誤</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Rule_Action</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Rule_事件中文</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Exchange</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>分析指紋</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>最近執行</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>FinBERT_Title</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>分析快取</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>原始Ticker</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker狀態</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker候選</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker核對依據</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker參照日期</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>上市狀態</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Ticker稽核警示</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>人工修改欄位</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>覆核註記</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>人工覆核人</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>人工覆核時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia, Broadcom shielded as AI power crunch hits chip supply chain, says Morgan Stanley</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>'-0.799</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOMF9lcTkxVU5OWUp5THhibUJWc3U0MWo5c2dreS02dFk3TGt4SlBXLVdpX0htOV85SnVsc3RUZjZJZDJac3p3bFgzS05uU2hjVXh5N0RjcFVtQml0TnBRSllwREVDdUVFOTBoTTRMT01RMnVUNGQtZk1ZY0ZIdUZHWHNBbjlaMk10dEpJZ3J5eTZHYjlDQW9JdEg4STBBLVNYNlFRb1J1aUJudHJkS2lmT0otSUJHdE5wVnJaXw?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>4e3dae046853cf51ec09ef5b</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>3b6b324abaa675f8751e2233</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr">
-        <is>
-          <t>NVDA-SUPPLY_CHAIN_DISRUPTION-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr"/>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH2" s="3" t="inlineStr"/>
-      <c r="BI2" s="3" t="inlineStr"/>
-      <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>EXCLUSIVE: Accenture contractor removed from FBI following damaging data breach, sources say</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.936</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPNnh4WEZTOEFBQUo1TmMzeGNFQ1FPaDQzY21NY0lpMjZJM2tiazlCSG5nb3BsdDVmaHVnc0RzbWpZZG1tUDBJdmNJN3pBcFN0eDdRTTlmZEt2YmZtck1Nc3ZzZTdzd1Ftb3FPNzVHcTFXQ2cxTGdXZHppeTlFUU5lSWxKY3ZmYnFtVWl6eGxueXFGaTBoVHd6WjUxSU80WkMyNE9pTkRHZnVyZ0tEN01pM0tCcHo1ZVdIOUpfRXVQaw?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>a4907b6d497dd82d98ff73f3</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>0c94db61ca0b7844387a6c13</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr">
-        <is>
-          <t>ACN-DATA_BREACH-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Exclusive | Electronic Arts Bondholders Allege Default Following Largest LBO</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>'-0.665</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZnpmM3d6Tjh4SVFKSF9VZ0l0SklwQU5lTmp5MUVSSnBwS0toY3RNdjU0R2thT0d6cVNON1BJaVExTUs3REI0UjgzOUdKcVRZNUZ1ZUZ2aWJZOFNDU1Z2Q1BaZDJOZDQ3bjNwT1ZNNnp2aE5iNlhsSmZYUmJEYlMyVXpfYWszYUk0SElxZmpGcnU2bjMyTFZpck51RGJvaUpIaGpnQ1JNdFBMNXFS?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="4" t="inlineStr">
-        <is>
-          <t>f575911bcbe6440ea649d1cd84a6a406</t>
-        </is>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>2e264a9236da31d2833fd839</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>ff3f385b58f0ac6dc49a5cd1</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr">
-        <is>
-          <t>EA-DEFAULT-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr"/>
-      <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:BL4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3861,355 +2984,806 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>NXP Semiconductors</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05T18:43:09+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Stifel：將恩智浦半導體目標價下調至265美元</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>分析師降評</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Accenture plc Class A Ordinary Shares (Ireland)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>EXCLUSIVE: Accenture contractor removed from FBI following damaging data breach, sources say</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>'-0.936</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPNnh4WEZTOEFBQUo1TmMzeGNFQ1FPaDQzY21NY0lpMjZJM2tiazlCSG5nb3BsdDVmaHVnc0RzbWpZZG1tUDBJdmNJN3pBcFN0eDdRTTlmZEt2YmZtck1Nc3ZzZTdzd1Ftb3FPNzVHcTFXQ2cxTGdXZHppeTlFUU5lSWxKY3ZmYnFtVWl6eGxueXFGaTBoVHd6WjUxSU80WkMyNE9pTkRHZnVyZ0tEN01pM0tCcHo1ZVdIOUpfRXVQaw?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>4e74d062a59940418686a4478b7b9cac</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>a4907b6d497dd82d98ff73f3</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>0c94db61ca0b7844387a6c13</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>ACN-DATA_BREACH-001</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.054</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2698307</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>ANALYST_DOWNGRADE</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>目標價下調</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>3de0fe66180c3ba2bf7ad865</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>89b3889fdbe9a159682df101</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>NXPI-ANALYST_DOWNGRADE-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>NXPI</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>NXPI</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr"/>
-      <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>BNY Mellon</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05T18:19:39+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>花旗：將紐約梅隆銀行目標價下調至160美元</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>分析師降評</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Exclusive | Electronic Arts Bondholders Allege Default Following Largest LBO</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>違約</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>'-0.665</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPZnpmM3d6Tjh4SVFKSF9VZ0l0SklwQU5lTmp5MUVSSnBwS0toY3RNdjU0R2thT0d6cVNON1BJaVExTUs3REI0UjgzOUdKcVRZNUZ1ZUZ2aWJZOFNDU1Z2Q1BaZDJOZDQ3bjNwT1ZNNnp2aE5iNlhsSmZYUmJEYlMyVXpfYWszYUk0SElxZmpGcnU2bjMyTFZpck51RGJvaUpIaGpnQ1JNdFBMNXFS?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>f575911bcbe6440ea649d1cd84a6a406</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>2e264a9236da31d2833fd839</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>ff3f385b58f0ac6dc49a5cd1</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>EA-DEFAULT-001</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.047</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2698288</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>ANALYST_DOWNGRADE</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>目標價下調</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>76d272247f249b3762e4eca7</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>7334a94113ef285cf816fb61</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>BNY-ANALYST_DOWNGRADE-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="BE3" s="2" t="inlineStr"/>
-      <c r="BF3" s="2" t="inlineStr"/>
-      <c r="BG3" s="2" t="inlineStr"/>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr"/>
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF3" s="4" t="inlineStr"/>
+      <c r="BG3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BL1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="65" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="65" customWidth="1" min="40" max="40"/>
+    <col width="22" customWidth="1" min="41" max="41"/>
+    <col width="22" customWidth="1" min="42" max="42"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="22" customWidth="1" min="44" max="44"/>
+    <col width="22" customWidth="1" min="45" max="45"/>
+    <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="48" max="48"/>
+    <col width="22" customWidth="1" min="49" max="49"/>
+    <col width="22" customWidth="1" min="50" max="50"/>
+    <col width="22" customWidth="1" min="51" max="51"/>
+    <col width="22" customWidth="1" min="52" max="52"/>
+    <col width="22" customWidth="1" min="53" max="53"/>
+    <col width="22" customWidth="1" min="54" max="54"/>
+    <col width="22" customWidth="1" min="55" max="55"/>
+    <col width="22" customWidth="1" min="56" max="56"/>
+    <col width="22" customWidth="1" min="57" max="57"/>
+    <col width="22" customWidth="1" min="58" max="58"/>
+    <col width="22" customWidth="1" min="59" max="59"/>
+    <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Published Time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>中文摘要</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>事件中文</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>最終判斷來源</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>分類狀態</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>已人工覆核</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>來源方法</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>FinBERT</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Rule_Event_Code</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Rule_Level</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>LLM事件代碼</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>LLM辨識公司</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker來源</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Title_ZH</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Event_type</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Event_Code</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>曝險金額</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>人工版本</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>article_id</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>news_id</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Event_ID</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>監控池</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Keyword候選</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Keyword事件代碼</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>LLM狀態</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>事件狀態</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Confirmed_Default</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>需要人工覆核</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>LLM模型</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt版本</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>API錯誤</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Rule_Action</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Rule_事件中文</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Exchange</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>分析指紋</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>最近執行</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>FinBERT_Title</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>分析快取</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>原始Ticker</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker狀態</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker候選</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker核對依據</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker參照日期</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>上市狀態</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-05.xlsx
+++ b/news_daily/2026-10-05.xlsx
@@ -1276,17 +1276,17 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1294,7 +1294,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1337,7 +1341,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1350,7 +1354,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>de09d14430c641b788d231939b362a57</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>156725e0076be977935fd03a</t>
@@ -1375,7 +1383,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1399,10 +1411,22 @@
       <c r="BF4" s="2" t="inlineStr"/>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2470,7 +2494,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -2526,7 +2554,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>6bfabfc66cad48b0b011c4fcebd3a967</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>156725e0076be977935fd03a</t>
@@ -2551,7 +2583,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2577,8 +2613,16 @@
       <c r="BH10" s="2" t="inlineStr"/>
       <c r="BI10" s="2" t="inlineStr"/>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL10"/>
